--- a/sources/标准汉语会话360句2_语法零基础版.xlsx
+++ b/sources/标准汉语会话360句2_语法零基础版.xlsx
@@ -4,9 +4,10 @@
   <workbookPr/>
   <sheets>
     <sheet name="01_语法总表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_学生练习版" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_按课索引" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_说明与来源" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="进阶练习" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_学生练习版" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_按课索引" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_说明与来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -15,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -26,8 +27,12 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +57,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B2A1F"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -277,6 +287,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -3064,6 +3075,1504 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="62" t="inlineStr">
+        <is>
+          <t>语法编号</t>
+        </is>
+      </c>
+      <c r="B1" s="62" t="inlineStr">
+        <is>
+          <t>课次</t>
+        </is>
+      </c>
+      <c r="C1" s="62" t="inlineStr">
+        <is>
+          <t>题型</t>
+        </is>
+      </c>
+      <c r="D1" s="62" t="inlineStr">
+        <is>
+          <t>题干</t>
+        </is>
+      </c>
+      <c r="E1" s="62" t="inlineStr">
+        <is>
+          <t>选项A</t>
+        </is>
+      </c>
+      <c r="F1" s="62" t="inlineStr">
+        <is>
+          <t>选项B</t>
+        </is>
+      </c>
+      <c r="G1" s="62" t="inlineStr">
+        <is>
+          <t>选项C</t>
+        </is>
+      </c>
+      <c r="H1" s="62" t="inlineStr">
+        <is>
+          <t>选项D</t>
+        </is>
+      </c>
+      <c r="I1" s="62" t="inlineStr">
+        <is>
+          <t>答案</t>
+        </is>
+      </c>
+      <c r="J1" s="62" t="inlineStr">
+        <is>
+          <t>解析（中文）</t>
+        </is>
+      </c>
+      <c r="K1" s="62" t="inlineStr">
+        <is>
+          <t>解析（英文）</t>
+        </is>
+      </c>
+      <c r="L1" s="62" t="inlineStr">
+        <is>
+          <t>题干（英文）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>360-2.1.1</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Do you like cats or dogs?</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr"/>
+      <c r="F2" s="14" t="inlineStr"/>
+      <c r="G2" s="14" t="inlineStr"/>
+      <c r="H2" s="14" t="inlineStr"/>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>你喜欢猫还是狗？</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr"/>
+      <c r="K2" s="14" t="inlineStr"/>
+      <c r="L2" s="14" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>360-2.1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Do you want baozi or dumplings?</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr"/>
+      <c r="F3" s="14" t="inlineStr"/>
+      <c r="G3" s="14" t="inlineStr"/>
+      <c r="H3" s="14" t="inlineStr"/>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>你要包子还是饺子？</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr"/>
+      <c r="K3" s="14" t="inlineStr"/>
+      <c r="L3" s="14" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>360-2.1.1</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Are you going today or tomorrow?</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr"/>
+      <c r="F4" s="14" t="inlineStr"/>
+      <c r="G4" s="14" t="inlineStr"/>
+      <c r="H4" s="14" t="inlineStr"/>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>你今天去还是明天去？</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr"/>
+      <c r="K4" s="14" t="inlineStr"/>
+      <c r="L4" s="14" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>360-2.1.2</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>I want to go skiing this weekend.</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr"/>
+      <c r="F5" s="14" t="inlineStr"/>
+      <c r="G5" s="14" t="inlineStr"/>
+      <c r="H5" s="14" t="inlineStr"/>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>这个周末我想去滑雪。</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr"/>
+      <c r="K5" s="14" t="inlineStr"/>
+      <c r="L5" s="14" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>360-2.1.2</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>I don't want to eat pizza.</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr"/>
+      <c r="F6" s="14" t="inlineStr"/>
+      <c r="G6" s="14" t="inlineStr"/>
+      <c r="H6" s="14" t="inlineStr"/>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>我不想吃比萨。</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr"/>
+      <c r="K6" s="14" t="inlineStr"/>
+      <c r="L6" s="14" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>360-2.2.1</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>The food at this Western restaurant tastes great.</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr"/>
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>这家西餐厅味道很好。</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr"/>
+      <c r="K7" s="14" t="inlineStr"/>
+      <c r="L7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>360-2.2.1</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>I have a headache.</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr"/>
+      <c r="F8" s="14" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr"/>
+      <c r="H8" s="14" t="inlineStr"/>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>我头疼。</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr"/>
+      <c r="K8" s="14" t="inlineStr"/>
+      <c r="L8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>360-2.2.1</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>I'm very busy with work.</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr"/>
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>我工作很忙。</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr"/>
+      <c r="K9" s="14" t="inlineStr"/>
+      <c r="L9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>360-2.2.2</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Is this dish spicy? (use the 不 question form)</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr"/>
+      <c r="F10" s="14" t="inlineStr"/>
+      <c r="G10" s="14" t="inlineStr"/>
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>这个菜辣不辣？</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr"/>
+      <c r="K10" s="14" t="inlineStr"/>
+      <c r="L10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>360-2.2.2</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Do you have time tomorrow? (use 有没有)</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
+      <c r="G11" s="14" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr"/>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>你明天有没有时间？</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr"/>
+      <c r="K11" s="14" t="inlineStr"/>
+      <c r="L11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>360-2.3.1</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>She cooks very well.</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr"/>
+      <c r="G12" s="14" t="inlineStr"/>
+      <c r="H12" s="14" t="inlineStr"/>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>她做饭做得很好。</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr"/>
+      <c r="K12" s="14" t="inlineStr"/>
+      <c r="L12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>360-2.3.1</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>He speaks Chinese very well.</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr"/>
+      <c r="G13" s="14" t="inlineStr"/>
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>他汉语说得很好。</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr"/>
+      <c r="K13" s="14" t="inlineStr"/>
+      <c r="L13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>360-2.3.1</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>He walks very slowly.</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr"/>
+      <c r="F14" s="14" t="inlineStr"/>
+      <c r="G14" s="14" t="inlineStr"/>
+      <c r="H14" s="14" t="inlineStr"/>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>他走得很慢。</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr"/>
+      <c r="K14" s="14" t="inlineStr"/>
+      <c r="L14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>360-2.3.2</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Can you ski?</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr"/>
+      <c r="F15" s="14" t="inlineStr"/>
+      <c r="G15" s="14" t="inlineStr"/>
+      <c r="H15" s="14" t="inlineStr"/>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>你会滑雪吗？</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr"/>
+      <c r="K15" s="14" t="inlineStr"/>
+      <c r="L15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>360-2.3.2</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>My mom can't cook.</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr"/>
+      <c r="F16" s="14" t="inlineStr"/>
+      <c r="G16" s="14" t="inlineStr"/>
+      <c r="H16" s="14" t="inlineStr"/>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>我妈妈不会做饭。</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr"/>
+      <c r="K16" s="14" t="inlineStr"/>
+      <c r="L16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>360-2.4.1</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Have you ever been to that ski resort?</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
+      <c r="G17" s="14" t="inlineStr"/>
+      <c r="H17" s="14" t="inlineStr"/>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>你去过那个滑雪场吗？</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="14" t="inlineStr"/>
+      <c r="L17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>360-2.4.1</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>I have never eaten baozi.</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr"/>
+      <c r="F18" s="14" t="inlineStr"/>
+      <c r="G18" s="14" t="inlineStr"/>
+      <c r="H18" s="14" t="inlineStr"/>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>我没吃过包子。</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr"/>
+      <c r="K18" s="14" t="inlineStr"/>
+      <c r="L18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>360-2.4.2</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Guess how old I am. (repeat the verb)</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr"/>
+      <c r="F19" s="14" t="inlineStr"/>
+      <c r="G19" s="14" t="inlineStr"/>
+      <c r="H19" s="14" t="inlineStr"/>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>你猜猜我多大。</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr"/>
+      <c r="K19" s="14" t="inlineStr"/>
+      <c r="L19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>360-2.4.2</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Can I try it? (repeat the verb)</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr"/>
+      <c r="F20" s="14" t="inlineStr"/>
+      <c r="G20" s="14" t="inlineStr"/>
+      <c r="H20" s="14" t="inlineStr"/>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>我可以试试吗？</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr"/>
+      <c r="K20" s="14" t="inlineStr"/>
+      <c r="L20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>360-2.5.1</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>He went skiing last weekend.</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr"/>
+      <c r="F21" s="14" t="inlineStr"/>
+      <c r="G21" s="14" t="inlineStr"/>
+      <c r="H21" s="14" t="inlineStr"/>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>他上个周末去滑雪了。</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr"/>
+      <c r="K21" s="14" t="inlineStr"/>
+      <c r="L21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>360-2.5.1</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>I ordered takeout today.</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr"/>
+      <c r="F22" s="14" t="inlineStr"/>
+      <c r="G22" s="14" t="inlineStr"/>
+      <c r="H22" s="14" t="inlineStr"/>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>我今天订外卖了。</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr"/>
+      <c r="K22" s="14" t="inlineStr"/>
+      <c r="L22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>360-2.5.1</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>He didn't go to work today.</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr"/>
+      <c r="F23" s="14" t="inlineStr"/>
+      <c r="G23" s="14" t="inlineStr"/>
+      <c r="H23" s="14" t="inlineStr"/>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>他今天没上班。</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr"/>
+      <c r="K23" s="14" t="inlineStr"/>
+      <c r="L23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>360-2.5.2</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>I'm going to the airport to see a friend off.</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr"/>
+      <c r="F24" s="14" t="inlineStr"/>
+      <c r="G24" s="14" t="inlineStr"/>
+      <c r="H24" s="14" t="inlineStr"/>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>我去机场送朋友。</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr"/>
+      <c r="K24" s="14" t="inlineStr"/>
+      <c r="L24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>360-2.5.2</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Let's go to the library to study.</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr"/>
+      <c r="F25" s="14" t="inlineStr"/>
+      <c r="G25" s="14" t="inlineStr"/>
+      <c r="H25" s="14" t="inlineStr"/>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>我们去图书馆学习吧。</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr"/>
+      <c r="K25" s="14" t="inlineStr"/>
+      <c r="L25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>360-2.5.3</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>My friend is treating me to a movie.</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr"/>
+      <c r="F26" s="14" t="inlineStr"/>
+      <c r="G26" s="14" t="inlineStr"/>
+      <c r="H26" s="14" t="inlineStr"/>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>朋友请我看电影。</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr"/>
+      <c r="K26" s="14" t="inlineStr"/>
+      <c r="L26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>360-2.5.3</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>The doctor told me to rest more.</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr"/>
+      <c r="F27" s="14" t="inlineStr"/>
+      <c r="G27" s="14" t="inlineStr"/>
+      <c r="H27" s="14" t="inlineStr"/>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>大夫让我多休息。</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr"/>
+      <c r="K27" s="14" t="inlineStr"/>
+      <c r="L27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>360-2.6.1</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>I have a bit of a fever.</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr"/>
+      <c r="F28" s="14" t="inlineStr"/>
+      <c r="G28" s="14" t="inlineStr"/>
+      <c r="H28" s="14" t="inlineStr"/>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>我有点儿发烧。</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr"/>
+      <c r="K28" s="14" t="inlineStr"/>
+      <c r="L28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>360-2.6.1</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>This dish is a little spicy.</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr"/>
+      <c r="F29" s="14" t="inlineStr"/>
+      <c r="G29" s="14" t="inlineStr"/>
+      <c r="H29" s="14" t="inlineStr"/>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>这个菜有点儿辣。</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr"/>
+      <c r="K29" s="14" t="inlineStr"/>
+      <c r="L29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>360-2.6.2</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>It isn't raining anymore.</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr"/>
+      <c r="F30" s="14" t="inlineStr"/>
+      <c r="G30" s="14" t="inlineStr"/>
+      <c r="H30" s="14" t="inlineStr"/>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>不下雨了。</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr"/>
+      <c r="K30" s="14" t="inlineStr"/>
+      <c r="L30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>360-2.6.2</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>I'm not hungry anymore.</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr"/>
+      <c r="F31" s="14" t="inlineStr"/>
+      <c r="G31" s="14" t="inlineStr"/>
+      <c r="H31" s="14" t="inlineStr"/>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>我不饿了。</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr"/>
+      <c r="K31" s="14" t="inlineStr"/>
+      <c r="L31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>360-2.6.2</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>My younger brother is ten now.</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr"/>
+      <c r="F32" s="14" t="inlineStr"/>
+      <c r="G32" s="14" t="inlineStr"/>
+      <c r="H32" s="14" t="inlineStr"/>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>我弟弟十岁了。</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr"/>
+      <c r="K32" s="14" t="inlineStr"/>
+      <c r="L32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>360-2.6.3</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>I have a fever, so I can't go work out today.</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr"/>
+      <c r="F33" s="14" t="inlineStr"/>
+      <c r="G33" s="14" t="inlineStr"/>
+      <c r="H33" s="14" t="inlineStr"/>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>我发烧了，今天不能去健身。</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr"/>
+      <c r="K33" s="14" t="inlineStr"/>
+      <c r="L33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>360-2.6.3</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Can you come tomorrow?</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr"/>
+      <c r="F34" s="14" t="inlineStr"/>
+      <c r="G34" s="14" t="inlineStr"/>
+      <c r="H34" s="14" t="inlineStr"/>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>你明天能来吗？</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr"/>
+      <c r="K34" s="14" t="inlineStr"/>
+      <c r="L34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>360-2.7.1</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>He is on the Internet right now.</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr"/>
+      <c r="F35" s="14" t="inlineStr"/>
+      <c r="G35" s="14" t="inlineStr"/>
+      <c r="H35" s="14" t="inlineStr"/>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>他正在上网呢。</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr"/>
+      <c r="K35" s="14" t="inlineStr"/>
+      <c r="L35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>360-2.7.1</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Mom is cooking right now.</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr"/>
+      <c r="F36" s="14" t="inlineStr"/>
+      <c r="G36" s="14" t="inlineStr"/>
+      <c r="H36" s="14" t="inlineStr"/>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>妈妈正在做饭呢。</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr"/>
+      <c r="K36" s="14" t="inlineStr"/>
+      <c r="L36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>360-2.7.2</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Mom made dumplings for me.</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr"/>
+      <c r="F37" s="14" t="inlineStr"/>
+      <c r="G37" s="14" t="inlineStr"/>
+      <c r="H37" s="14" t="inlineStr"/>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>妈妈给我做了饺子。</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr"/>
+      <c r="K37" s="14" t="inlineStr"/>
+      <c r="L37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>360-2.7.2</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Please sing a song for us.</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+      <c r="F38" s="14" t="inlineStr"/>
+      <c r="G38" s="14" t="inlineStr"/>
+      <c r="H38" s="14" t="inlineStr"/>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>请给我们唱个歌吧。</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr"/>
+      <c r="K38" s="14" t="inlineStr"/>
+      <c r="L38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>360-2.7.3</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>I have to go to the airport to pick up a friend.</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+      <c r="F39" s="14" t="inlineStr"/>
+      <c r="G39" s="14" t="inlineStr"/>
+      <c r="H39" s="14" t="inlineStr"/>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>我得去机场接朋友。</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr"/>
+      <c r="K39" s="14" t="inlineStr"/>
+      <c r="L39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>360-2.7.3</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>You don't have to come tomorrow.</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+      <c r="F40" s="14" t="inlineStr"/>
+      <c r="G40" s="14" t="inlineStr"/>
+      <c r="H40" s="14" t="inlineStr"/>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>你明天不用来。</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr"/>
+      <c r="K40" s="14" t="inlineStr"/>
+      <c r="L40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>360-2.8.1</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>This cake is cheaper than that one.</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+      <c r="F41" s="14" t="inlineStr"/>
+      <c r="G41" s="14" t="inlineStr"/>
+      <c r="H41" s="14" t="inlineStr"/>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>这个蛋糕比那个便宜。</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr"/>
+      <c r="K41" s="14" t="inlineStr"/>
+      <c r="L41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>360-2.8.1</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>My dog is not as fat as your dog.</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+      <c r="F42" s="14" t="inlineStr"/>
+      <c r="G42" s="14" t="inlineStr"/>
+      <c r="H42" s="14" t="inlineStr"/>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>我的狗没有你的狗胖。</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr"/>
+      <c r="K42" s="14" t="inlineStr"/>
+      <c r="L42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>360-2.8.2</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>It's more than ten degrees below zero today.</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr"/>
+      <c r="F43" s="14" t="inlineStr"/>
+      <c r="G43" s="14" t="inlineStr"/>
+      <c r="H43" s="14" t="inlineStr"/>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>今天零下十多度。</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr"/>
+      <c r="K43" s="14" t="inlineStr"/>
+      <c r="L43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>360-2.8.2</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>My dad is over fifty.</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr"/>
+      <c r="F44" s="14" t="inlineStr"/>
+      <c r="G44" s="14" t="inlineStr"/>
+      <c r="H44" s="14" t="inlineStr"/>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>我爸爸五十多岁。</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr"/>
+      <c r="K44" s="14" t="inlineStr"/>
+      <c r="L44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>360-2.8.2</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>This watermelon is a little over three jin.</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr"/>
+      <c r="F45" s="14" t="inlineStr"/>
+      <c r="G45" s="14" t="inlineStr"/>
+      <c r="H45" s="14" t="inlineStr"/>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>这个西瓜三斤多。</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr"/>
+      <c r="K45" s="14" t="inlineStr"/>
+      <c r="L45" s="14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4796,7 +6305,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5031,13 +6540,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5188,6 +6697,18 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>进阶练习（网站，2026-10）</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>「进阶练习」表：本册学生是零基础，选择题读不懂，所以网站上的语法练习只保留英译汉（看英文、想中文、再看答案自评）。本表是每个语法点完整的翻译题清单（每点 2–3 道，覆盖本册全部语法点；原有翻译题经核对后保留或修改，不足的已补充），网站只用这里的题，01 表「练习1–3」中的填空/选择/排序等题不再显示。01 表原有练习未改动。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
